--- a/inventory_by_bunker/BUNKER 2927 Monclova.xlsx
+++ b/inventory_by_bunker/BUNKER 2927 Monclova.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bunker de Refacciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7D1A3E1-F4FC-4BC6-8114-32717EEBF210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE147BC6-FA0E-4035-83A8-351BFC64D369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A9822A03-8A7F-4E73-A9BC-4BBF4B6E15FD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="78">
   <si>
     <t>Cantidad</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Descripción</t>
-  </si>
-  <si>
     <t>Fabricante</t>
   </si>
   <si>
@@ -59,45 +56,18 @@
     <t>Serie</t>
   </si>
   <si>
-    <t>Condición</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Nuevo</t>
   </si>
   <si>
-    <t>Fusor</t>
-  </si>
-  <si>
-    <t>Kit de mantenimiento</t>
-  </si>
-  <si>
     <t>HP</t>
   </si>
   <si>
     <t>M806</t>
   </si>
   <si>
-    <t>Ensamble</t>
-  </si>
-  <si>
     <t>Fusser Drive Assembly</t>
   </si>
   <si>
-    <t>Teclado y Mouse</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Disco</t>
-  </si>
-  <si>
-    <t>Disco SSD</t>
-  </si>
-  <si>
     <t>Kingston</t>
   </si>
   <si>
@@ -149,9 +119,6 @@
     <t>Cat6</t>
   </si>
   <si>
-    <t>Caja Hermética</t>
-  </si>
-  <si>
     <t>CFPWR4CIG</t>
   </si>
   <si>
@@ -164,12 +131,6 @@
     <t>FS</t>
   </si>
   <si>
-    <t>Clavija</t>
-  </si>
-  <si>
-    <t>Clavija Nema</t>
-  </si>
-  <si>
     <t>L5-15</t>
   </si>
   <si>
@@ -179,9 +140,6 @@
     <t>Bryant</t>
   </si>
   <si>
-    <t>Telefono</t>
-  </si>
-  <si>
     <t>Telefono Analogo</t>
   </si>
   <si>
@@ -194,18 +152,9 @@
     <t>Mouse</t>
   </si>
   <si>
-    <t>basculas</t>
-  </si>
-  <si>
     <t>bizerba</t>
   </si>
   <si>
-    <t>xc115</t>
-  </si>
-  <si>
-    <t>buen estado</t>
-  </si>
-  <si>
     <t>Impresora</t>
   </si>
   <si>
@@ -221,15 +170,9 @@
     <t>X2NC027903</t>
   </si>
   <si>
-    <t>Scanner Manual</t>
-  </si>
-  <si>
     <t>DS8108</t>
   </si>
   <si>
-    <t>impresora laser</t>
-  </si>
-  <si>
     <t>Impresora Laser</t>
   </si>
   <si>
@@ -254,9 +197,6 @@
     <t>8CN110011N</t>
   </si>
   <si>
-    <t>Bascula &amp; Escaner</t>
-  </si>
-  <si>
     <t>Bascula</t>
   </si>
   <si>
@@ -272,29 +212,74 @@
     <t>F18I11787</t>
   </si>
   <si>
-    <t>impresora termica</t>
-  </si>
-  <si>
     <t>XXZUN253502422</t>
   </si>
   <si>
-    <t>zq620</t>
-  </si>
-  <si>
-    <t>nueva</t>
-  </si>
-  <si>
     <t>Zebra</t>
   </si>
   <si>
     <t>Eaton</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Kit de Mantenimiento</t>
+  </si>
+  <si>
+    <t>Teclado Administrativo</t>
+  </si>
+  <si>
+    <t>Disco Duro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD </t>
+  </si>
+  <si>
+    <t>Caja Hermetica</t>
+  </si>
+  <si>
+    <t>Bascula Etiquetadora</t>
+  </si>
+  <si>
+    <t>Funcional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clavija </t>
+  </si>
+  <si>
+    <t>Clavija de Seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contacto de Seguridad </t>
+  </si>
+  <si>
+    <t>XC115</t>
+  </si>
+  <si>
+    <t>Escaner Manual</t>
+  </si>
+  <si>
+    <t>HP 806</t>
+  </si>
+  <si>
+    <t>Bascula / Escaner</t>
+  </si>
+  <si>
+    <t>ZQ620</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Condicion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,26 +288,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -334,7 +322,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,11 +336,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF8EA9DB"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -360,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -368,29 +362,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,9 +407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -449,7 +447,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -555,7 +553,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -697,7 +695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -705,679 +703,704 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78A0DC9-9B87-48BF-A871-0B83C3393732}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.90625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="22" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>2</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>2</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="B18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>2</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
-        <v>30</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
-        <v>2</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="B20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="8">
+        <v>20226010550595</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6">
+        <v>1</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="9">
+        <v>22012010561885</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6">
+        <v>1</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
+        <v>1</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
+        <v>1</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6">
+        <v>1</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6">
+        <v>1</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6">
+        <v>1</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6">
+        <v>1</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6">
+        <v>1</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
-        <v>2</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
-        <v>1</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>5</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>1</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="C30" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>1</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="6">
-        <v>20226010550595</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>1</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="7">
-        <v>22012010561885</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>1</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22">
-        <v>806</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>1</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>1</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>1</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>1</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>1</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>1</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>1</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>80</v>
+      <c r="G30" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1396,6 +1419,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="32ac5903-15cb-4ea5-b5ff-0c3789514317" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DA39339B156F48BF44A94205EFD080" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9a9a01d537a2fce1fca5d9c9f5be1c83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="455f0459-8915-4426-a819-a99675e21b2b" xmlns:ns4="32ac5903-15cb-4ea5-b5ff-0c3789514317" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="209341808fbe9bf1b0fc2176103ea180" ns3:_="" ns4:_="">
     <xsd:import namespace="455f0459-8915-4426-a819-a99675e21b2b"/>
@@ -1634,14 +1665,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="32ac5903-15cb-4ea5-b5ff-0c3789514317" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F9A557E-8D80-40F8-8E10-FBB9CA9F63F1}">
   <ds:schemaRefs>
@@ -1651,6 +1674,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49472576-712C-4B45-B0EB-A2D71EDE5A61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="455f0459-8915-4426-a819-a99675e21b2b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="32ac5903-15cb-4ea5-b5ff-0c3789514317"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD57EA4B-DD4B-4640-B8DB-C11597FFA693}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1667,21 +1707,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49472576-712C-4B45-B0EB-A2D71EDE5A61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="455f0459-8915-4426-a819-a99675e21b2b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="32ac5903-15cb-4ea5-b5ff-0c3789514317"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>